--- a/pipeline/credit_rating/output/sniratings_xhtn_20260924.xlsx
+++ b/pipeline/credit_rating/output/sniratings_xhtn_20260924.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:35</t>
+          <t>2026-09-24 08:43:55</t>
         </is>
       </c>
       <c r="R2" s="1" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:35</t>
+          <t>2026-09-24 08:43:55</t>
         </is>
       </c>
       <c r="R3" s="1" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:35</t>
+          <t>2026-09-24 08:43:55</t>
         </is>
       </c>
       <c r="R4" s="1" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:35</t>
+          <t>2026-09-24 08:43:55</t>
         </is>
       </c>
       <c r="R5" s="1" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:35</t>
+          <t>2026-09-24 08:43:55</t>
         </is>
       </c>
       <c r="R6" s="1" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:35</t>
+          <t>2026-09-24 08:43:55</t>
         </is>
       </c>
       <c r="R7" s="1" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:35</t>
+          <t>2026-09-24 08:43:55</t>
         </is>
       </c>
       <c r="R8" s="1" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:35</t>
+          <t>2026-09-24 08:43:55</t>
         </is>
       </c>
       <c r="R9" s="1" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:35</t>
+          <t>2026-09-24 08:43:55</t>
         </is>
       </c>
       <c r="R10" s="1" t="n">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:35</t>
+          <t>2026-09-24 08:43:55</t>
         </is>
       </c>
       <c r="R11" s="1" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:35</t>
+          <t>2026-09-24 08:43:55</t>
         </is>
       </c>
       <c r="R12" s="1" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:35</t>
+          <t>2026-09-24 08:43:55</t>
         </is>
       </c>
       <c r="R13" s="1" t="n">

--- a/pipeline/credit_rating/output/sniratings_xhtn_20260924.xlsx
+++ b/pipeline/credit_rating/output/sniratings_xhtn_20260924.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="R2" s="1" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="R3" s="1" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="R4" s="1" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="R5" s="1" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="R6" s="1" t="n">
@@ -925,7 +925,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="R7" s="1" t="n">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="R8" s="1" t="n">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="R9" s="1" t="n">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="R10" s="1" t="n">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="R11" s="1" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="R12" s="1" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:55</t>
+          <t>2026-09-24 13:44:31</t>
         </is>
       </c>
       <c r="R13" s="1" t="n">
